--- a/excel_config/yunxing_params/平衡设计.xlsx
+++ b/excel_config/yunxing_params/平衡设计.xlsx
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>{"hp_max":230,"mp_max":40,"physical_atk":17.5,"magic_atk":20,"physical_def":16,"magic_def":19,"spd":92,"control_power":50,"control_resist":60}</t>
+          <t>{"hp_max": 230, "mp_max": 40, "physical_atk": 17.5, "magic_atk": 20, "physical_def": 16, "magic_def": 19, "spd": 92, "control_power": 50, "control_resist": 60}</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>{"hp_max":260,"mp_max":80,"physical_atk":19,"magic_atk":22,"physical_def":18,"magic_def":22,"spd":98,"control_power":80,"control_resist":90}</t>
+          <t>{"hp_max": 260, "mp_max": 80, "physical_atk": 19, "magic_atk": 22, "physical_def": 18, "magic_def": 22, "spd": 98, "control_power": 80, "control_resist": 90}</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>{"hp_max":310,"mp_max":100,"physical_atk":34,"magic_atk":38,"physical_def":26,"magic_def":31,"spd":108,"control_power":105,"control_resist":110}</t>
+          <t>{"hp_max": 310, "mp_max": 100, "physical_atk": 34, "magic_atk": 38, "physical_def": 26, "magic_def": 31, "spd": 108, "control_power": 105, "control_resist": 110}</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>{"body":5}</t>
+          <t>{"body": 5}</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>{"spirit":5}</t>
+          <t>{"spirit": 5}</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>{"body":3}</t>
+          <t>{"body": 3}</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>{"spirit":2.4,"sense":0.8}</t>
+          <t>{"spirit": 2.4, "sense": 0.8}</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>{"body":2}</t>
+          <t>{"body": 2}</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>{"spirit":1.2,"sense":1.2}</t>
+          <t>{"spirit": 1.2, "sense": 1.2}</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>{"agility":3,"sense":2}</t>
+          <t>{"agility": 3, "sense": 2}</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>{"sense":3,"spirit":1}</t>
+          <t>{"sense": 3, "spirit": 1}</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>{"sense":2,"body":1}</t>
+          <t>{"sense": 2, "body": 1}</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>{"body":0.05}</t>
+          <t>{"body": 0.05}</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>{"spirit":0.04,"sense":0.01}</t>
+          <t>{"spirit": 0.04, "sense": 0.01}</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>{"body":2}</t>
+          <t>{"body": 2}</t>
         </is>
       </c>
     </row>
@@ -1934,47 +1934,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -2034,47 +2034,47 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>{"early":30,"mid":40,"late":50}</t>
+          <t>{"early": 30, "mid": 40, "late": 50}</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>{"early":100,"mid":120,"late":140}</t>
+          <t>{"early": 100, "mid": 120, "late": 140}</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>{"early":300,"mid":360,"late":420}</t>
+          <t>{"early": 300, "mid": 360, "late": 420}</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>{"early":800,"mid":960,"late":1120}</t>
+          <t>{"early": 800, "mid": 960, "late": 1120}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>{"early":2000,"mid":2400,"late":2800}</t>
+          <t>{"early": 2000, "mid": 2400, "late": 2800}</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>{"early":5000,"mid":6000,"late":7000}</t>
+          <t>{"early": 5000, "mid": 6000, "late": 7000}</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>{"early":12000,"mid":14400,"late":16800}</t>
+          <t>{"early": 12000, "mid": 14400, "late": 16800}</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>{"early":30000,"mid":36000,"late":42000}</t>
+          <t>{"early": 30000, "mid": 36000, "late": 42000}</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>{"single":80000}</t>
+          <t>{"single": 80000}</t>
         </is>
       </c>
       <c r="L5" s="4" t="n"/>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>{"low":0.85,"medium":1,"high":1.25,"supreme":1.55}</t>
+          <t>{"low": 0.85, "medium": 1, "high": 1.25, "supreme": 1.55}</t>
         </is>
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>{"1":"lianqi","2":"zhuji","3":"jindan","4":"yuanying","5":"huashen","6":"lianxu","7":"heti","8":"dacheng","9":"dujie"}</t>
+          <t>{"1": "lianqi", "2": "zhuji", "3": "jindan", "4": "yuanying", "5": "huashen", "6": "lianxu", "7": "heti", "8": "dacheng", "9": "dujie"}</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>{"body":10,"spirit":10,"sense":10,"agility":10}</t>
+          <t>{"body": 10, "spirit": 10, "sense": 10, "agility": 10}</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>{"body":13,"spirit":13,"sense":13,"agility":13}</t>
+          <t>{"body": 13, "spirit": 13, "sense": 13, "agility": 13}</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>{"body":16,"spirit":16,"sense":16,"agility":16}</t>
+          <t>{"body": 16, "spirit": 16, "sense": 16, "agility": 16}</t>
         </is>
       </c>
     </row>
